--- a/data/trans_camb/P1418-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1418-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>0,61</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,63</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 0,0</t>
+          <t>-0,84; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,98</t>
+          <t>-0,33; 1,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 5,3</t>
+          <t>-0,33; 4,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,45</t>
+          <t>-1,37; 0,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,62; -0,19</t>
+          <t>-1,63; -0,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 5,03</t>
+          <t>-0,6; 3,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,11</t>
+          <t>-0,76; 0,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,14</t>
+          <t>-0,76; 0,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 3,07</t>
+          <t>-0,21; 2,37</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>475,09%</t>
+          <t>400,29%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>127,71%</t>
+          <t>101,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>200,74%</t>
+          <t>166,88%</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 1767,25</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,57</t>
+          <t>-0,58</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,72</t>
+          <t>-1,71</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,03</t>
+          <t>-1,06</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,34</t>
+          <t>-1,46; 0,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,53; -0,0</t>
+          <t>-1,6; -0,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 0,32</t>
+          <t>-1,43; 0,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,56; -0,37</t>
+          <t>-3,47; -0,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 0,09</t>
+          <t>-3,13; 0,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,44; -0,1</t>
+          <t>-3,38; -0,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,01; -0,27</t>
+          <t>-1,93; -0,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,94; -0,17</t>
+          <t>-1,9; -0,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,0; -0,17</t>
+          <t>-1,98; -0,18</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-68,1%</t>
+          <t>-69,84%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-63,22%</t>
+          <t>-62,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-60,75%</t>
+          <t>-62,3%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 136,74</t>
+          <t>-100,0; 114,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 133,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 551,67</t>
+          <t>-100,0; 348,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-88,88; -12,12</t>
+          <t>-88,09; -7,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-84,01; 11,98</t>
+          <t>-82,06; 29,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-91,23; 6,87</t>
+          <t>-89,19; 7,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-82,91; -15,52</t>
+          <t>-82,0; -7,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-83,68; -7,27</t>
+          <t>-82,88; -9,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-87,47; -5,54</t>
+          <t>-86,7; -5,34</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,9</t>
+          <t>-0,96</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,15</t>
+          <t>-1,94</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,59</t>
+          <t>-1,52</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,94; -0,18</t>
+          <t>-2,73; -0,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,37; -1,07</t>
+          <t>-3,25; -1,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 0,52</t>
+          <t>-2,36; 0,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 0,81</t>
+          <t>-3,55; 1,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,09; -0,77</t>
+          <t>-4,95; -0,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,54; -0,22</t>
+          <t>-4,12; 0,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,74; -0,13</t>
+          <t>-2,78; 0,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,62; -1,31</t>
+          <t>-3,81; -1,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,91; -0,36</t>
+          <t>-2,85; -0,25</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-46,86%</t>
+          <t>-50,12%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-39,52%</t>
+          <t>-35,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-42,27%</t>
+          <t>-40,46%</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-94,98; 33,16</t>
+          <t>-100,0; 24,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,37 +1225,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-87,03; 68,17</t>
+          <t>-85,81; 51,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-55,97; 25,86</t>
+          <t>-53,24; 28,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-73,88; -12,15</t>
+          <t>-73,95; -15,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-65,1; -3,12</t>
+          <t>-60,2; 3,34</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-62,02; -3,1</t>
+          <t>-62,52; 1,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-79,41; -42,49</t>
+          <t>-81,74; -41,49</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-64,73; -11,49</t>
+          <t>-61,46; -4,37</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-2,14</t>
+          <t>-0,98</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,85</t>
+          <t>-2,08</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,27</t>
+          <t>-1,48</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,9; -1,13</t>
+          <t>-5,88; -1,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,07; -1,23</t>
+          <t>-5,88; -1,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 0,35</t>
+          <t>-3,96; 1,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,23; -0,42</t>
+          <t>-7,12; -0,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,43; -3,12</t>
+          <t>-9,28; -3,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 1,42</t>
+          <t>-5,36; 0,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,01; -1,5</t>
+          <t>-5,48; -1,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,75; -2,88</t>
+          <t>-6,71; -2,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,03; -0,12</t>
+          <t>-3,66; 0,41</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-42,15%</t>
+          <t>-19,32%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-18,75%</t>
+          <t>-21,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-30,39%</t>
+          <t>-19,81%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-85,34; -20,93</t>
+          <t>-86,45; -26,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-86,24; -27,23</t>
+          <t>-85,17; -27,26</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-79,96; 7,34</t>
+          <t>-56,66; 42,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-60,46; -4,38</t>
+          <t>-61,67; -7,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-77,22; -35,44</t>
+          <t>-77,06; -38,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-43,07; 19,78</t>
+          <t>-44,71; 11,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-65,87; -24,85</t>
+          <t>-62,37; -19,4</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-75,73; -44,3</t>
+          <t>-76,1; -43,63</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-58,1; -1,82</t>
+          <t>-41,24; 6,97</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-6,53</t>
+          <t>-6,73</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,75</t>
+          <t>-1,85</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-4,18</t>
+          <t>-4,3</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,06; -4,88</t>
+          <t>-12,04; -5,1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-12,37; -5,76</t>
+          <t>-12,21; -5,48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,28; -3,43</t>
+          <t>-10,58; -3,17</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 5,93</t>
+          <t>-3,51; 5,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 1,95</t>
+          <t>-6,22; 2,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 1,88</t>
+          <t>-5,72; 1,56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,2; -0,51</t>
+          <t>-6,2; -0,5</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-8,06; -2,61</t>
+          <t>-8,18; -2,75</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,93; -1,6</t>
+          <t>-6,63; -1,71</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-56,09%</t>
+          <t>-57,79%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-14,67%</t>
+          <t>-15,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-35,48%</t>
+          <t>-36,5%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-84,57; -50,01</t>
+          <t>-84,54; -49,73</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-87,64; -56,9</t>
+          <t>-87,6; -53,83</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-71,45; -33,69</t>
+          <t>-73,0; -34,44</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-25,57; 59,85</t>
+          <t>-24,89; 60,03</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-45,95; 21,16</t>
+          <t>-43,3; 24,79</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-37,13; 21,79</t>
+          <t>-38,6; 16,36</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-47,13; -5,26</t>
+          <t>-47,05; -5,69</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-59,98; -25,1</t>
+          <t>-61,07; -26,3</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-50,09; -15,26</t>
+          <t>-50,2; -18,01</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-6,57</t>
+          <t>-6,97</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-15,33</t>
+          <t>-10,73</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-11,28</t>
+          <t>-9,1</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 0,5</t>
+          <t>-10,16; 0,88</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-13,31; -3,63</t>
+          <t>-13,67; -4,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-10,79; -2,06</t>
+          <t>-12,0; -2,61</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 3,05</t>
+          <t>-8,81; 3,17</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-13,39; -1,88</t>
+          <t>-13,65; -2,39</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-24,56; -9,36</t>
+          <t>-15,58; -5,77</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 0,54</t>
+          <t>-8,68; 0,43</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-12,36; -4,54</t>
+          <t>-12,45; -4,7</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-17,19; -7,71</t>
+          <t>-12,55; -5,34</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-44,1%</t>
+          <t>-46,77%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-64,44%</t>
+          <t>-45,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-57,3%</t>
+          <t>-46,23%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-56,71; 4,66</t>
+          <t>-57,18; 7,23</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-76,65; -30,13</t>
+          <t>-76,15; -32,95</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-61,5; -16,62</t>
+          <t>-63,76; -21,43</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-34,14; 14,81</t>
+          <t>-33,62; 16,14</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-49,75; -8,29</t>
+          <t>-51,53; -10,96</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-87,78; -41,91</t>
+          <t>-57,92; -28,46</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-36,28; 3,0</t>
+          <t>-38,38; 3,35</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-55,77; -24,64</t>
+          <t>-55,48; -25,85</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-77,59; -41,93</t>
+          <t>-57,04; -31,85</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-6,1</t>
+          <t>-5,82</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-5,2</t>
+          <t>-5,12</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-5,7</t>
+          <t>-5,55</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-11,18; 4,11</t>
+          <t>-11,59; 3,19</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-14,71; -1,26</t>
+          <t>-15,12; -1,34</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-12,59; -0,06</t>
+          <t>-12,38; 0,7</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 11,56</t>
+          <t>-2,78; 11,02</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-15,39; -0,69</t>
+          <t>-14,35; -0,59</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-11,95; 0,67</t>
+          <t>-11,65; 0,99</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 6,75</t>
+          <t>-4,36; 6,13</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-13,43; -2,83</t>
+          <t>-13,51; -2,97</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-10,6; -1,24</t>
+          <t>-10,26; -1,12</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-28,51%</t>
+          <t>-27,2%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-16,51%</t>
+          <t>-16,24%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-20,63%</t>
+          <t>-20,1%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-45,12; 24,39</t>
+          <t>-45,61; 18,22</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-59,14; -6,45</t>
+          <t>-60,14; -9,69</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-49,04; -0,54</t>
+          <t>-47,32; 4,63</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 42,52</t>
+          <t>-8,16; 40,13</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-41,92; -1,98</t>
+          <t>-40,93; -2,2</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-33,06; 2,25</t>
+          <t>-32,13; 2,85</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-14,41; 27,09</t>
+          <t>-14,31; 24,06</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-44,4; -11,21</t>
+          <t>-43,59; -11,89</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-34,29; -4,99</t>
+          <t>-32,85; -4,32</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-1,44</t>
+          <t>-1,23</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-1,87</t>
+          <t>-1,33</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-1,63</t>
+          <t>-1,25</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,24; -1,4</t>
+          <t>-3,32; -1,35</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,94; -2,1</t>
+          <t>-4,01; -2,17</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,61; -0,4</t>
+          <t>-2,27; -0,26</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 1,29</t>
+          <t>-1,98; 1,02</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,33; -1,57</t>
+          <t>-4,53; -1,57</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,49; -0,41</t>
+          <t>-2,68; -0,02</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,21; -0,49</t>
+          <t>-2,23; -0,38</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,9; -2,21</t>
+          <t>-3,87; -2,15</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,65; -0,71</t>
+          <t>-2,08; -0,38</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-26,43%</t>
+          <t>-22,42%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-18,4%</t>
+          <t>-13,05%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-20,81%</t>
+          <t>-15,92%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-54,87; -27,79</t>
+          <t>-55,75; -27,55</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-65,98; -42,71</t>
+          <t>-66,86; -43,06</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-44,33; -8,25</t>
+          <t>-38,04; -5,53</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-16,13; 14,11</t>
+          <t>-17,69; 10,78</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-39,81; -15,61</t>
+          <t>-41,07; -17,04</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-32,99; -4,63</t>
+          <t>-24,06; -0,03</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-26,54; -6,29</t>
+          <t>-26,72; -4,96</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-45,74; -29,68</t>
+          <t>-46,79; -29,05</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-32,45; -10,04</t>
+          <t>-25,02; -5,12</t>
         </is>
       </c>
     </row>
